--- a/Docs/原版适配裁决表_蛊手牌系统.xlsx
+++ b/Docs/原版适配裁决表_蛊手牌系统.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\STS2-GuZhenRenRubild\GuZhenRenRebuild\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC4B210-18AA-4624-ADCC-5ED5621642AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A03A86-7249-4556-8F05-E7A115853A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="262">
   <si>
     <t>ID</t>
   </si>
@@ -478,9 +478,6 @@
     <t>战斗边界</t>
   </si>
   <si>
-    <t>玩家死亡时是否补齐蛊牌堆清理</t>
-  </si>
-  <si>
     <t>CombatManager.cs:923-938 只清 5 个原生牌堆；PlayerCombatState.cs:142-151 战后 AllPiles.Clear 兜底</t>
   </si>
   <si>
@@ -542,9 +539,6 @@
   </si>
   <si>
     <t>接受原版 UnplayableReason</t>
-  </si>
-  <si>
-    <t>追加模组气泡说明（参照 XianYuanWarningPatch）</t>
   </si>
   <si>
     <t>§9</t>
@@ -818,6 +812,18 @@
   </si>
   <si>
     <t>D-10</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家死亡时是否补齐蛊牌堆清理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加模组气泡说明（参照 XianYuanWarningPatch）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1389,7 +1395,7 @@
         <v>29</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P2" s="5"/>
     </row>
@@ -1437,7 +1443,7 @@
         <v>41</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P3" s="5"/>
     </row>
@@ -1485,7 +1491,7 @@
         <v>41</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P4" s="5"/>
     </row>
@@ -1533,7 +1539,7 @@
         <v>61</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P5" s="5"/>
     </row>
@@ -1581,7 +1587,7 @@
         <v>73</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P6" s="5"/>
     </row>
@@ -1629,7 +1635,7 @@
         <v>73</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P7" s="5"/>
     </row>
@@ -1677,7 +1683,7 @@
         <v>92</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P8" s="11"/>
     </row>
@@ -1725,13 +1731,13 @@
         <v>100</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.15">
       <c r="A10" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>17</v>
@@ -1773,13 +1779,13 @@
         <v>109</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.15">
       <c r="A11" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>110</v>
@@ -1820,7 +1826,9 @@
       <c r="N11" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="O11" s="5"/>
+      <c r="O11" s="11" t="s">
+        <v>259</v>
+      </c>
       <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.15">
@@ -1866,7 +1874,11 @@
       <c r="N12" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="O12" s="5"/>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>A，滤空时回退放行原版候选（已落地 5609c7b）</t>
+        </is>
+      </c>
       <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.15">
@@ -1912,7 +1924,11 @@
       <c r="N13" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="O13" s="5"/>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>A，角色卡池=蛊池，事件给牌一律给蛊（已固化 479294a）</t>
+        </is>
+      </c>
       <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16" ht="24" x14ac:dyDescent="0.15">
@@ -1958,7 +1974,11 @@
       <c r="N14" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="O14" s="5"/>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>蛊牌不可附魔（随D-05）；仙蛊不可克隆；普通蛊克隆继承母本转数（e9efa3e）</t>
+        </is>
+      </c>
       <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.15">
@@ -1971,26 +1991,26 @@
       <c r="C15" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>26</v>
@@ -2002,41 +2022,45 @@
         <v>60</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="O15" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>B，死亡时四个蛊牌堆并入清理（已落地 494a029）</t>
+        </is>
+      </c>
       <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16" ht="24" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>26</v>
@@ -2048,41 +2072,45 @@
         <v>60</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="O16" s="5"/>
+        <v>164</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>A，蛊牌堆对其他人物隐藏（已落地 186fe3f）</t>
+        </is>
+      </c>
       <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16" ht="24" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>172</v>
+      <c r="H17" s="11" t="s">
+        <v>261</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>71</v>
@@ -2094,41 +2122,45 @@
         <v>60</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="O17" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>B，追加模组气泡说明，参照仙元提示（已落地 6885590）</t>
+        </is>
+      </c>
       <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16" ht="24" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>46</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>71</v>
@@ -2142,39 +2174,43 @@
       <c r="N18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="O18" s="5"/>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>随D-05关闭——蛊牌无法附魔，卡面问题不存在（266cc3d）</t>
+        </is>
+      </c>
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16" ht="36" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>80</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>26</v>
@@ -2186,9 +2222,13 @@
         <v>28</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="O19" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>A，认可无色卡不做代码适配（266cc3d）</t>
+        </is>
+      </c>
       <c r="P19" s="5"/>
     </row>
   </sheetData>
@@ -2222,179 +2262,179 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>138</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>217</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>148</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="24" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>230</v>
-      </c>
       <c r="F9" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2456,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B1" s="15"/>
     </row>
@@ -2426,18 +2466,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
@@ -2446,10 +2486,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
@@ -2458,7 +2498,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B8" s="10"/>
     </row>
@@ -2467,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
@@ -2475,15 +2515,15 @@
         <v>4</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
@@ -2491,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
@@ -2499,7 +2539,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
@@ -2507,7 +2547,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
@@ -2515,15 +2555,15 @@
         <v>12</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
@@ -2532,10 +2572,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
